--- a/data/trans_dic/IP25B_1_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP25B_1_R-Estudios-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,39; 50,28</t>
+          <t>18,12; 49,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,68; 32,19</t>
+          <t>13,18; 33,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,42; 38,09</t>
+          <t>19,48; 38,55</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20,82; 43,44</t>
+          <t>21,08; 42,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,25; 34,06</t>
+          <t>23,08; 33,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,17; 34,71</t>
+          <t>23,25; 33,88</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,05; 21,68</t>
+          <t>11,24; 21,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,11; 23,01</t>
+          <t>11,72; 22,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,93; 20,3</t>
+          <t>13,16; 20,29</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,29; 35,39</t>
+          <t>20,35; 35,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,71; 28,44</t>
+          <t>20,88; 28,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,76; 30,05</t>
+          <t>21,62; 29,61</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10138; 26290</t>
+          <t>9472; 26020</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7790; 19772</t>
+          <t>8096; 20388</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22077; 43313</t>
+          <t>22156; 43832</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>93784; 195642</t>
+          <t>94947; 193177</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>119055; 174440</t>
+          <t>118220; 170252</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>223027; 334114</t>
+          <t>223811; 326113</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16241; 31864</t>
+          <t>16521; 32259</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21984; 41755</t>
+          <t>21272; 40687</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>42452; 66680</t>
+          <t>43226; 66645</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>131769; 229914</t>
+          <t>132181; 231256</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>156383; 214708</t>
+          <t>157692; 216130</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>305590; 422051</t>
+          <t>303692; 415858</t>
         </is>
       </c>
     </row>
